--- a/ig/main/ValueSet-jdv-resultat-qualitatif-cisis.xlsx
+++ b/ig/main/ValueSet-jdv-resultat-qualitatif-cisis.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="61">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260311144903</t>
+    <t>20260420150250</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-11T14:49:03+01:00</t>
+    <t>2026-04-20T15:02:50+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -105,13 +105,16 @@
     <t>positif(-ive)</t>
   </si>
   <si>
-    <t>en attente</t>
-  </si>
-  <si>
-    <t>positif – séroconversion</t>
-  </si>
-  <si>
-    <t>positif-multiplication par 4</t>
+    <t>1290194006</t>
+  </si>
+  <si>
+    <t>séroconversion</t>
+  </si>
+  <si>
+    <t>1396170002</t>
+  </si>
+  <si>
+    <t>multiplication par 4 des IgG</t>
   </si>
   <si>
     <t>260385009</t>
@@ -120,13 +123,10 @@
     <t>négatif(-ive)</t>
   </si>
   <si>
-    <t>douteux</t>
-  </si>
-  <si>
     <t>373068000</t>
   </si>
   <si>
-    <t>non déterminé(e)</t>
+    <t>indéterminé(e)</t>
   </si>
   <si>
     <t>125154007</t>
@@ -459,7 +459,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -492,129 +492,121 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="B19" t="s" s="2">
         <v>60</v>
       </c>
     </row>
